--- a/Assets/Resources/StatusData.xlsx
+++ b/Assets/Resources/StatusData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monke\Desktop\war_LIke2\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFAF314E-053C-4E86-9A97-9BF2C0AFAD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CA48CE-FFCD-4776-A745-49CEC3D814D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C74F93A7-7243-4DE6-AFA9-670647F89833}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>StatusData</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,43 +39,75 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxHP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>avoid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>attackDistance</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>player</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>npc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>homeLess</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>soldier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>injurySoldier</t>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOMELESS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOLDIER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INJURYSOLDIER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Stats</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Stats</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attackBonus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpBonus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dodgeBonus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rangeBonus</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -109,7 +141,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -118,13 +150,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -158,30 +196,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,326 +526,423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9823CD2-1276-4E69-9F2D-16012AE5A2BE}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="7" width="15.5625" customWidth="1"/>
+    <col min="1" max="11" width="15.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="J5" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6">
-        <v>100</v>
-      </c>
-      <c r="D3" s="6">
-        <v>100</v>
-      </c>
-      <c r="E3" s="6">
-        <v>20</v>
-      </c>
-      <c r="F3" s="6">
-        <v>5</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6">
-        <v>80</v>
-      </c>
-      <c r="D4" s="6">
-        <v>80</v>
-      </c>
-      <c r="E4" s="6">
-        <v>15</v>
-      </c>
-      <c r="F4" s="6">
-        <v>2</v>
-      </c>
-      <c r="G4" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6">
-        <v>120</v>
-      </c>
-      <c r="D5" s="6">
-        <v>120</v>
-      </c>
-      <c r="E5" s="6">
-        <v>25</v>
-      </c>
-      <c r="F5" s="6">
-        <v>7</v>
-      </c>
-      <c r="G5" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6">
-        <v>35</v>
-      </c>
-      <c r="D6" s="6">
-        <v>120</v>
-      </c>
-      <c r="E6" s="6">
-        <v>13</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.6">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="3">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/StatusData.xlsx
+++ b/Assets/Resources/StatusData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monke\Desktop\war_LIke2\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CA48CE-FFCD-4776-A745-49CEC3D814D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A25B83-0E68-43C9-9EF8-578491DF0C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C74F93A7-7243-4DE6-AFA9-670647F89833}"/>
   </bookViews>
@@ -25,28 +25,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>StatusData</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>characterType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>attackDistance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>npc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,18 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HOMELESS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOLDIER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INJURYSOLDIER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Bonus Stats</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,6 +84,46 @@
   </si>
   <si>
     <t>rangeBonus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노숙자 김헌일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일병 장윤성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈영병 김윤재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>굶주린 모녀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인신매매범 권범</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -206,10 +222,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,161 +542,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9823CD2-1276-4E69-9F2D-16012AE5A2BE}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="11" width="15.5625" customWidth="1"/>
+    <col min="1" max="10" width="15.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A3" s="2" t="s">
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
         <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>5</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J5" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -689,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -700,37 +705,72 @@
       <c r="J6" s="1">
         <v>0</v>
       </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -741,9 +781,8 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -754,9 +793,8 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -767,9 +805,8 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -780,9 +817,8 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -793,9 +829,8 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -806,9 +841,8 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -819,9 +853,8 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -832,9 +865,8 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -845,9 +877,8 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -858,9 +889,8 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -871,9 +901,8 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -884,9 +913,8 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -897,9 +925,8 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -910,9 +937,8 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -923,9 +949,8 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -936,13 +961,12 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/StatusData.xlsx
+++ b/Assets/Resources/StatusData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monke\Desktop\war_LIke2\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A25B83-0E68-43C9-9EF8-578491DF0C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC739E6B-13FE-4822-82DB-5607A16CF55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C74F93A7-7243-4DE6-AFA9-670647F89833}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>StatusData</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,6 +124,18 @@
   </si>
   <si>
     <t>선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더미봇</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,16 +783,36 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.6">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>10</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" s="1"/>
